--- a/output/pdf_financials_xlsx/FTU.xlsx
+++ b/output/pdf_financials_xlsx/FTU.xlsx
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.233982</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.424714</v>
       </c>
     </row>
     <row r="35">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.233982</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.424714</v>
       </c>
     </row>
     <row r="37">
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>15.63018</v>
+        <v>15.396198</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>13.664285</v>
+        <v>12.239571</v>
       </c>
     </row>
     <row r="49">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">

--- a/output/pdf_financials_xlsx/FTU.xlsx
+++ b/output/pdf_financials_xlsx/FTU.xlsx
@@ -491,15 +491,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -525,15 +521,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.156273</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.151377</v>
       </c>
     </row>
     <row r="8">
@@ -542,15 +534,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -559,15 +547,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0.037493</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.040943</v>
       </c>
     </row>
     <row r="10">
@@ -576,15 +560,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.334049</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.391613</v>
       </c>
     </row>
     <row r="11">
@@ -610,15 +590,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -627,15 +603,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -644,15 +616,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -661,15 +629,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -695,15 +659,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -763,15 +723,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -780,15 +736,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -882,15 +834,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1870,15 +1818,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -1887,15 +1831,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0.004221</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>-0.005151</v>
       </c>
     </row>
     <row r="102">
@@ -1904,15 +1844,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -1921,15 +1857,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -1938,15 +1870,11 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.000976</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>-0.002059</v>
       </c>
     </row>
     <row r="105">
@@ -1955,15 +1883,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -1972,15 +1896,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.005197</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.00721</v>
       </c>
     </row>
     <row r="107">
@@ -1989,15 +1909,11 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2006,15 +1922,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2023,15 +1935,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2040,15 +1948,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2057,15 +1961,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2074,15 +1974,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2091,15 +1987,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2108,15 +2000,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2125,15 +2013,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>1.885625</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>2.569939</v>
       </c>
     </row>
     <row r="116">
@@ -2142,15 +2026,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2159,15 +2039,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2176,15 +2052,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2193,15 +2065,11 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0.011984</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>0.047269</v>
       </c>
     </row>
     <row r="120">
@@ -2210,15 +2078,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2227,15 +2091,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2244,15 +2104,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2261,15 +2117,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2278,15 +2130,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2295,15 +2143,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2312,15 +2156,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2346,15 +2186,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2363,15 +2199,11 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>-1.422197</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>-1.386082</v>
       </c>
     </row>
     <row r="130">
@@ -2380,15 +2212,11 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.294149</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.233982</v>
       </c>
     </row>
     <row r="131">
@@ -2397,15 +2225,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2414,15 +2238,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.060167</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>1.190732</v>
       </c>
     </row>
     <row r="133">
@@ -2431,15 +2251,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.233982</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>1.424714</v>
       </c>
     </row>
     <row r="134">
@@ -2448,15 +2264,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2465,15 +2277,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>1.350046</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>2.529545</v>
       </c>
     </row>
   </sheetData>
@@ -2487,7 +2295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2996,6 +2804,2066 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in net assets attributable to holders</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in net assets attributable to holders of redeemable Class A shares</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Adjustment for</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Distributions on Preferred shares</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" s="5" t="n">
+        <v>1.463714</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>1.358981</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Adjustment for</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Unrealized (gain) loss in the value of currency</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" s="5" t="n">
+        <v>-0.011984</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.047269</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Adjustment for</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Net realized (gain) loss on investments and derivatives</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" s="5" t="n">
+        <v>-0.711362</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-1.311029</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Net change in unrealized appreciation/depreciation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Net change in unrealized appreciation/depreciation of investments and derivatives</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" s="5" t="n">
+        <v>-3.71848</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.015295</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Net change in unrealized appreciation/depreciation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>(Gain) loss on remeasurement of Preferred shares</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" s="5" t="n">
+        <v>2.960859</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-1.965695</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Net change in unrealized appreciation/depreciation</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Purchase of investments, net of option premiums</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" s="5" t="n">
+        <v>-0.523523</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-0.083467</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Net change in unrealized appreciation/depreciation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Proceeds from sale of investments</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>1.885625</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>2.569939</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Net change in unrealized appreciation/depreciation</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>(Increase) decrease in interest, dividends and other receivables</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.004221</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-0.005151</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Net change in unrealized appreciation/depreciation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in fees and other accounts payable</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.000976</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-0.002059</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Net change in unrealized appreciation/depreciation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) operating activities</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.350046</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2.529545</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Distributions paid on Preferred shares</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" s="5" t="n">
+        <v>-1.422197</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>-1.386082</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>-1.422197</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>-1.386082</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Unrealized gain (loss) in the value of currency</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" s="5" t="n">
+        <v>0.011984</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.047269</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Net increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>-0.060167</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>1.190732</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cash at beginning of the year</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.294149</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.233982</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cash at end of the year</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0.233982</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>1.424714</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dividends received, net of withholding taxes*</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" s="5" t="n">
+        <v>0.313232</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.288459</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cash flows from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Interest received *</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0.012177</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Schedule of Portfolio Investments</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>As at November</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2,600 American Express Company</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" s="5" t="n">
+        <v>0.555474</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0.242221</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>20,600 Bank of America Corp.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" s="5" t="n">
+        <v>1.057048</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.588813</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>8,000 Bank of New York Mellon Corp.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" s="5" t="n">
+        <v>0.497811</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0.263272</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>9,800 Citigroup Inc.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" s="5" t="n">
+        <v>0.643165</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.748479</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1,500 CME Group Inc.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" s="5" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0.100398</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>18,000 Fifth Third Bancorp.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" s="5" t="n">
+        <v>0.887274</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0.379658</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2,400 Goldman Sachs Group Inc.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" s="5" t="n">
+        <v>1.256402</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0.557037</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>4,300 J.P. Morgan Chase &amp; Co.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" s="5" t="n">
+        <v>0.805518</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.354927</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>10,400 Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" s="5" t="n">
+        <v>1.312213</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.655352</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>4,200 PNC Financial Services Group Inc.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" s="5" t="n">
+        <v>0.958058</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.405453</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>20,000 Regions Financial Corp.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" s="5" t="n">
+        <v>0.629313</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0.222332</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>9,000 State Street Corp.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" s="5" t="n">
+        <v>0.972073</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.52516</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>10,381 Truist Financial Corporation</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" s="5" t="n">
+        <v>0.658776</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0.456352</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4,600 US Bancorp</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" s="5" t="n">
+        <v>0.283061</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0.210358</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>U.S. Common Equities</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>6,623 Wells Fargo &amp; Co.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" s="5" t="n">
+        <v>0.430531</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0.338784</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Total Foreign Common Equities</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Total Foreign Common Equities in Core Holdings (92.7%)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" s="5" t="n">
+        <v>11.305637</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>6.048596</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Other U.S. Common Equity Holdings</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>4,900 Metlife Inc.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" s="5" t="n">
+        <v>0.50951</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0.240893</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Other U.S. Common Equity Holdings</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>20,224 Huntington Bancshares Inc.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" s="5" t="n">
+        <v>0.424424</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0.198635</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Other U.S. Common Equity Holdings</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Total Other U.S. Common Equities (7.7%)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
+        <v>0.933934</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.439528</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Other U.S. Common Equity Holdings</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Total Foreign Common Equities (100.4%)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" s="5" t="n">
+        <v>12.239571</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>6.488124</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Schedule of Portfolio Investments (continued...)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>As at November</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>No. of contracts   U.S. call options written</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>(5) American Express Co. @ $145 December 2022</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" s="5" t="n">
+        <v>-0.009065999999999999</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>-0.003525</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>No. of contracts   U.S. call options written</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>(20) Bank of America Corp. @ $39 January 2023</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" s="5" t="n">
+        <v>-0.002888</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>-0.002902</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>No. of contracts   U.S. call options written</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>(20) Bank of New York Mellon Corp. @ $45 January 2023</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" s="5" t="n">
+        <v>-0.006779</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>-0.005437</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>No. of contracts   U.S. call options written</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>(10) Citigroup Inc. @ $50 January 2023</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" s="5" t="n">
+        <v>-0.002142</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>-0.002711</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>No. of contracts   U.S. call options written</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>(5) J.P. Morgan Chase &amp; Co. @ $135 January 2023</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" s="5" t="n">
+        <v>-0.004881</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>-0.003491</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>No. of contracts   U.S. call options written</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>(5) MetLife Inc. @ $70 December 2022</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" s="5" t="n">
+        <v>-0.004711</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>-0.001491</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>No. of contracts   U.S. call options written</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>(20) Morgan Stanley @ $92.50 January 2023</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" s="5" t="n">
+        <v>-0.01254</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>-0.00873</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>No. of contracts   U.S. call options written</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>(5) US Bancorp. @ $45 January 2023</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" s="5" t="n">
+        <v>-0.001254</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>-0.000712</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>No. of contracts   U.S. call options written</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>(5) Wells Fargo &amp; Co. @ $50 January 2023</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>-0.000853</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>-0.000666</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>No. of contracts   U.S. call options written</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Total U.S. call options written (-0.4%)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" s="5" t="n">
+        <v>-0.045114</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>-0.029665</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>No. of contracts   U.S. call options written</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>No. of contracts   U.S. call options written total</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" s="5" t="n">
+        <v>12.194457</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>6.458459</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Less adjustments for transaction costs                  (4,546)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Total Investments (100.0%)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>12.194457</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>6.453913</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Net gain (loss) on investments and derivatives</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Net realized gain (loss)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" s="5" t="n">
+        <v>0.711362</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>1.311029</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Net gain (loss) on investments and derivatives</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Net change in unrealized appreciation/depreciation</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>3.71848</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>-2.015295</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Net gain (loss) on investments and derivatives</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Dividends</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" s="5" t="n">
+        <v>0.363287</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0.408408</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Net gain (loss) on investments and derivatives</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Interest for distribution purposes</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0.012177</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Net gain (loss) on investments and derivatives</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Net gain (loss) on investments and derivatives</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="n">
+        <v>4.793129</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>-0.283681</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Other gain (loss)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Realized gain (loss) on currency</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" s="5" t="n">
+        <v>-0.046491</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>0.021311</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Other gain (loss)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Change in unrealized gain (loss) in the value of currency</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" s="5" t="n">
+        <v>0.011984</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0.047269</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Other gain (loss)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Other gain (loss) total</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" s="5" t="n">
+        <v>4.758622</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>-0.215101</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Management fees</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0.101208</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Audit fees</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" s="5" t="n">
+        <v>0.018272</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0.021332</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Directors’ fees</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>0.023583</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0.022025</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Independent Review Committee fees</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" s="5" t="n">
+        <v>0.004268</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0.004077</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Custodial fees</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" s="5" t="n">
+        <v>0.021291</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.019112</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Legal fees</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>0.01979</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.028144</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Shareholder reporting costs</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
+        <v>0.013191</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.009586000000000001</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Other operating expenses</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.037493</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0.040943</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Harmonized sales tax</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>0.026806</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.02599</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Transaction costs</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" s="5" t="n">
+        <v>0.002187</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>0.004441</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Witholding taxes</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" s="5" t="n">
+        <v>0.054268</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>0.114755</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>0.334049</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>0.391613</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>of redeemable Class A shares before distributions</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>of redeemable Class A shares before distributions and remeasurement on Preferred shares</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" s="5" t="n">
+        <v>4.424573</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>-0.606714</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>of redeemable Class A shares before distributions</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Distributions on Preferred shares</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>-1.463714</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>-1.358981</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>of redeemable Class A shares before distributions</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Gain (loss) on remeasurement of Preferred shares (note 2)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" s="5" t="n">
+        <v>-2.960859</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>1.965695</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in net assets attributable to holders</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in net assets attributable to holders of redeemable Class A shares</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in net assets attributable to holders</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in net assets attributable to holders per redeemable Class A share (note 10)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Net assets attributable to holders of redeemable</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Class A shares - Beginning of year</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Net assets attributable to holders of redeemable</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in net assets attributable to holders of redeemable Class A shares</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Net assets attributable to holders of redeemable</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Class A shares</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Net assets attributable to holders of redeemable</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Net Assets attributable to holders of redeemable Class A shares - End of year</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
